--- a/data/trans_orig/IMC_inf_MED_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC medido en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2012 (tasa de respuesta: 70,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12632</t>
+          <t>12921</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13186</t>
+          <t>13255</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>10736</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22500</t>
+          <t>22837</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11352</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20494</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>13984</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25860</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19232</t>
+          <t>19194</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25029</t>
+          <t>25299</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41771</t>
+          <t>41307</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20692</t>
+          <t>20753</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33316</t>
+          <t>33336</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21207</t>
+          <t>21671</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33761</t>
+          <t>34177</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45235</t>
+          <t>45575</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63452</t>
+          <t>62932</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,25%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3177</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11105</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26963</t>
+          <t>26832</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44492</t>
+          <t>45897</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49824</t>
+          <t>49745</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74934</t>
+          <t>74181</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83139</t>
+          <t>83658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111579</t>
+          <t>112928</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28567</t>
+          <t>27763</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47859</t>
+          <t>46670</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31953</t>
+          <t>32373</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51499</t>
+          <t>51711</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>65066</t>
+          <t>64574</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>92563</t>
+          <t>92639</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57670</t>
+          <t>57392</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81081</t>
+          <t>81795</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>73514</t>
+          <t>73022</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>100441</t>
+          <t>100318</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>138034</t>
+          <t>137846</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>172877</t>
+          <t>174937</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>149474</t>
+          <t>150246</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>178143</t>
+          <t>179872</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129540</t>
+          <t>129898</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>157954</t>
+          <t>160855</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>286916</t>
+          <t>288215</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>329412</t>
+          <t>332236</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>50,09%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16931</t>
+          <t>16941</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20399</t>
+          <t>20542</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17044</t>
+          <t>17205</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32978</t>
+          <t>33142</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>7088</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17428</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>20782</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17626</t>
+          <t>18002</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34170</t>
+          <t>34118</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>16947</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22195</t>
+          <t>22067</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18394</t>
+          <t>18489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34767</t>
+          <t>35652</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20286</t>
+          <t>20387</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35632</t>
+          <t>36009</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26167</t>
+          <t>26607</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42277</t>
+          <t>43395</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>51324</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74112</t>
+          <t>72900</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,74%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58082</t>
+          <t>56875</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76101</t>
+          <t>75181</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43209</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61203</t>
+          <t>61619</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>106857</t>
+          <t>105636</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>133759</t>
+          <t>132731</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>9644</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43134</t>
+          <t>43209</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65908</t>
+          <t>66764</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69590</t>
+          <t>70535</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98470</t>
+          <t>99280</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>120392</t>
+          <t>120929</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>157111</t>
+          <t>157733</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>43932</t>
+          <t>44112</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>66385</t>
+          <t>67086</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>52062</t>
+          <t>52333</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>76269</t>
+          <t>77735</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>102971</t>
+          <t>101827</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>136866</t>
+          <t>134450</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100942</t>
+          <t>101983</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>132154</t>
+          <t>132384</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>117486</t>
+          <t>119429</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>150375</t>
+          <t>151274</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>228045</t>
+          <t>228942</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>272126</t>
+          <t>272780</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>239245</t>
+          <t>238786</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>275693</t>
+          <t>273811</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>204826</t>
+          <t>205466</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>242093</t>
+          <t>242372</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>456760</t>
+          <t>455428</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>510896</t>
+          <t>505536</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,4%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11757</t>
+          <t>11796</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24977</t>
+          <t>25641</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25432</t>
+          <t>25549</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26228</t>
+          <t>26243</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45965</t>
+          <t>45561</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC medido en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2016 (tasa de respuesta: 69,19%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12665</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>16825</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9361</t>
+          <t>9431</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9162</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14710</t>
+          <t>14796</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15095</t>
+          <t>15053</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>9188</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20010</t>
+          <t>20443</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18431</t>
+          <t>18084</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32182</t>
+          <t>32709</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,37%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12844</t>
+          <t>13427</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23176</t>
+          <t>23219</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15483</t>
+          <t>15631</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26763</t>
+          <t>26798</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31475</t>
+          <t>31604</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46528</t>
+          <t>46619</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,26%</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>8447</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11920</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24594</t>
+          <t>23921</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26237</t>
+          <t>25603</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44393</t>
+          <t>43937</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40755</t>
+          <t>40841</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63051</t>
+          <t>63098</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18938</t>
+          <t>18696</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33625</t>
+          <t>34241</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38280</t>
+          <t>38114</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58815</t>
+          <t>58660</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62630</t>
+          <t>60659</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90210</t>
+          <t>86024</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63245</t>
+          <t>61959</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87182</t>
+          <t>86298</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64102</t>
+          <t>63787</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89551</t>
+          <t>88728</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>134045</t>
+          <t>133894</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>168953</t>
+          <t>168731</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>191466</t>
+          <t>191581</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>220310</t>
+          <t>219538</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>158050</t>
+          <t>158420</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>189099</t>
+          <t>190119</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>357845</t>
+          <t>356509</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>399143</t>
+          <t>399258</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>9174</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20815</t>
+          <t>20775</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18052</t>
+          <t>17131</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34649</t>
+          <t>33517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30013</t>
+          <t>30398</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49948</t>
+          <t>51142</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>13205</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>13816</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10622</t>
+          <t>11215</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23501</t>
+          <t>23307</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>13371</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16718</t>
+          <t>16238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11934</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>26385</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>11549</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24660</t>
+          <t>24033</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27215</t>
+          <t>27256</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43231</t>
+          <t>42957</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>42366</t>
+          <t>42303</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>63319</t>
+          <t>63357</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67577</t>
+          <t>67263</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>83474</t>
+          <t>83204</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52091</t>
+          <t>52861</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69289</t>
+          <t>71070</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>123260</t>
+          <t>123781</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>148147</t>
+          <t>149305</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,64%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9031</t>
+          <t>9500</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>13785</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21614</t>
+          <t>21581</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39029</t>
+          <t>38340</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>40180</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60517</t>
+          <t>62316</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64485</t>
+          <t>65191</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93991</t>
+          <t>93129</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29891</t>
+          <t>29645</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49880</t>
+          <t>49464</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>52271</t>
+          <t>51503</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>76235</t>
+          <t>77241</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>87414</t>
+          <t>86894</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>118821</t>
+          <t>116293</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>87388</t>
+          <t>88337</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>116286</t>
+          <t>118264</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>109532</t>
+          <t>108368</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>141471</t>
+          <t>141606</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>204838</t>
+          <t>207218</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>248558</t>
+          <t>249326</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>282753</t>
+          <t>281515</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>315904</t>
+          <t>317666</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>236539</t>
+          <t>235991</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>273474</t>
+          <t>273740</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>527949</t>
+          <t>527304</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>580503</t>
+          <t>580139</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,36%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13288</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26973</t>
+          <t>27036</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22712</t>
+          <t>23259</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>41742</t>
+          <t>41507</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>40131</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>62936</t>
+          <t>62772</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC medido en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2023 (tasa de respuesta: 78,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>758</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>911</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8642</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>13991</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10990</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23249</t>
+          <t>22853</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>47,7%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16765</t>
+          <t>16533</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9584</t>
+          <t>9631</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19115</t>
+          <t>19140</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18042</t>
+          <t>18495</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32425</t>
+          <t>32272</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,36%</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19017</t>
+          <t>18965</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>13438</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28182</t>
+          <t>28021</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20824</t>
+          <t>20128</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40604</t>
+          <t>40343</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17718</t>
+          <t>17593</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22707</t>
+          <t>22241</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42377</t>
+          <t>41613</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31984</t>
+          <t>30719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56666</t>
+          <t>55488</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12561</t>
+          <t>11940</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>31031</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34623</t>
+          <t>36073</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63116</t>
+          <t>64139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>51302</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>86709</t>
+          <t>86440</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110551</t>
+          <t>111544</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>145318</t>
+          <t>147929</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88870</t>
+          <t>89391</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117818</t>
+          <t>116510</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>207851</t>
+          <t>205683</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>263104</t>
+          <t>265628</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>68,31%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12453</t>
+          <t>12132</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23758</t>
+          <t>23437</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12396</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29584</t>
+          <t>30140</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>578</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1391</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7248</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>10839</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17112</t>
+          <t>17117</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>18726</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>8684</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21334</t>
+          <t>20941</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19196</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36712</t>
+          <t>35898</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36051</t>
+          <t>36543</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49282</t>
+          <t>50029</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43672</t>
+          <t>44187</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58435</t>
+          <t>58293</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>83821</t>
+          <t>84926</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103822</t>
+          <t>104469</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>73,06%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2314</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>9800</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>466</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20211</t>
+          <t>19790</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16619</t>
+          <t>16449</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31634</t>
+          <t>32357</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25607</t>
+          <t>25521</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46496</t>
+          <t>46311</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>11093</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26758</t>
+          <t>25482</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29386</t>
+          <t>30560</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>51839</t>
+          <t>51710</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44477</t>
+          <t>44292</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>72374</t>
+          <t>72222</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28760</t>
+          <t>29483</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>58536</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54543</t>
+          <t>52697</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>86087</t>
+          <t>85587</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>88510</t>
+          <t>88903</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>132065</t>
+          <t>130675</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>161830</t>
+          <t>162355</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>205963</t>
+          <t>203026</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>150833</t>
+          <t>152681</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>184544</t>
+          <t>185940</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>324130</t>
+          <t>324081</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>381194</t>
+          <t>385899</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>66,56%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6912</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19048</t>
+          <t>20331</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25924</t>
+          <t>26386</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21244</t>
+          <t>20647</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42481</t>
+          <t>40962</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_inf_MED_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R-Estudios-trans_orig.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC recogido por medición en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2012 (tasa de respuesta: 83,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,19 +735,19 @@
         <v>8035</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>4606</v>
+        <v>4070</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>13544</v>
+        <v>12845</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.1412122558927119</v>
+        <v>0.1060393065377344</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.08095092929389716</v>
+        <v>0.05371545232758473</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.2380398602802858</v>
+        <v>0.1695196754063182</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>12</v>
@@ -756,19 +756,19 @@
         <v>7680</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>4228</v>
+        <v>4286</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>12573</v>
+        <v>13086</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.1165306953184245</v>
+        <v>0.09532122096204139</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.06415503548807323</v>
+        <v>0.05319660103506962</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1907676573824504</v>
+        <v>0.1624154142118086</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>24</v>
@@ -777,19 +777,19 @@
         <v>15715</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>10532</v>
+        <v>10343</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>22507</v>
+        <v>22093</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.1279663698798589</v>
+        <v>0.1005158003622646</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.0857631954919864</v>
+        <v>0.06615437444791718</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.1832734037025253</v>
+        <v>0.1413102044512711</v>
       </c>
     </row>
     <row r="5">
@@ -800,67 +800,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>7316</v>
+        <v>10556</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>4011</v>
+        <v>6106</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>12679</v>
+        <v>16476</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.1285746338948912</v>
+        <v>0.139312307564914</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.07048705782002618</v>
+        <v>0.08058165277544602</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.2228403586116651</v>
+        <v>0.2174365573267125</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>6559</v>
+        <v>7861</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>3407</v>
+        <v>4110</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>11266</v>
+        <v>13564</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.09951971969356405</v>
+        <v>0.09756607857992444</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.05169409539890064</v>
+        <v>0.05100986753590755</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1709351662094329</v>
+        <v>0.1683533279364876</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>13875</v>
+        <v>18417</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>8910</v>
+        <v>12656</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>20950</v>
+        <v>26782</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.1129816943615241</v>
+        <v>0.1177986191386808</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.07255085291741996</v>
+        <v>0.08094703794004916</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.1705953262765718</v>
+        <v>0.1713005925256955</v>
       </c>
     </row>
     <row r="6">
@@ -871,67 +871,67 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>13427</v>
+        <v>16697</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>8803</v>
+        <v>10874</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>19278</v>
+        <v>23334</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.2359767536969392</v>
+        <v>0.2203531699350827</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.1547095725746198</v>
+        <v>0.1435070369748532</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.3388098663266883</v>
+        <v>0.3079512141738985</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>19432</v>
+        <v>23711</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>14032</v>
+        <v>17668</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>25718</v>
+        <v>31422</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.2948380881539987</v>
+        <v>0.2942843966740684</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.2129074517694956</v>
+        <v>0.2192792103587136</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3902205352878531</v>
+        <v>0.3899972632445399</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>32858</v>
+        <v>40407</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>25010</v>
+        <v>31937</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>41658</v>
+        <v>50440</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.2675659445196162</v>
+        <v>0.2584532191060782</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.2036553173444647</v>
+        <v>0.2042766214930462</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.3392205322314222</v>
+        <v>0.3226254221673713</v>
       </c>
     </row>
     <row r="7">
@@ -942,67 +942,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>27493</v>
+        <v>39857</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>21313</v>
+        <v>32582</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>33781</v>
+        <v>46801</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4831948789001926</v>
+        <v>0.5260039340046733</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.3745758487601319</v>
+        <v>0.4299909254285665</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.5936963360382552</v>
+        <v>0.6176527074738907</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>26642</v>
+        <v>35725</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>19977</v>
+        <v>28293</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>33315</v>
+        <v>43071</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4042372289849627</v>
+        <v>0.4434017993121296</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.3031137945499205</v>
+        <v>0.3511558288601094</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.5054861961247327</v>
+        <v>0.5345686286878685</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>54135</v>
+        <v>75582</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>44723</v>
+        <v>64334</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>62755</v>
+        <v>85145</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.4408205716730621</v>
+        <v>0.4834353803334877</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.3641824529926468</v>
+        <v>0.4114907323260825</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.511013912100845</v>
+        <v>0.5446049530248588</v>
       </c>
     </row>
     <row r="8">
@@ -1022,16 +1022,16 @@
         <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>3238</v>
+        <v>3194</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.01104147761526505</v>
+        <v>0.008291281957595651</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.05690687560621139</v>
+        <v>0.0421459429512858</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>9</v>
@@ -1040,19 +1040,19 @@
         <v>5594</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>2593</v>
+        <v>2389</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>10440</v>
+        <v>9481</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.08487426784905003</v>
+        <v>0.06942650447183624</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.03933804490542252</v>
+        <v>0.0296514475667081</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1584122901951468</v>
+        <v>0.1176683294696853</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>10</v>
@@ -1061,19 +1061,19 @@
         <v>6222</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>3025</v>
+        <v>3173</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>10898</v>
+        <v>10557</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.05066541956593872</v>
+        <v>0.03979698105948872</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.02463147369519592</v>
+        <v>0.02029715710714419</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.08873892021352475</v>
+        <v>0.06752260070017171</v>
       </c>
     </row>
     <row r="9">
@@ -1084,16 +1084,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>56899</v>
+        <v>75773</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>56899</v>
+        <v>75773</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>56899</v>
+        <v>75773</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1105,16 +1105,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>65906</v>
+        <v>80571</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>65906</v>
+        <v>80571</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>65906</v>
+        <v>80571</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -1126,16 +1126,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>177</v>
+        <v>224</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>122805</v>
+        <v>156343</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>122805</v>
+        <v>156343</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>122805</v>
+        <v>156343</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -1165,19 +1165,19 @@
         <v>61950</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>50819</v>
+        <v>49954</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>75098</v>
+        <v>74612</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.1787640033547511</v>
+        <v>0.1506802707079595</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.1466434987771967</v>
+        <v>0.1215027194391034</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.2167030929906764</v>
+        <v>0.1814777527749722</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>52</v>
@@ -1186,19 +1186,19 @@
         <v>35220</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>27524</v>
+        <v>27183</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>44992</v>
+        <v>45735</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1111883542088791</v>
+        <v>0.0934861423804577</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.08689324339974698</v>
+        <v>0.07215336257022238</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1420369595376202</v>
+        <v>0.1213957268457873</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>138</v>
@@ -1207,19 +1207,19 @@
         <v>97170</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>83212</v>
+        <v>82540</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>113022</v>
+        <v>114063</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.1464933807306001</v>
+        <v>0.1233315603987697</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.125450196562031</v>
+        <v>0.1047626577986812</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.1703926485322844</v>
+        <v>0.1447722343822388</v>
       </c>
     </row>
     <row r="11">
@@ -1230,67 +1230,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>40876</v>
+        <v>51064</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>33033</v>
+        <v>40100</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>51973</v>
+        <v>62837</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.1179522941602499</v>
+        <v>0.124203099028444</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.09532032375341813</v>
+        <v>0.09753598748221222</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.149973112100743</v>
+        <v>0.1528385343431685</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>37320</v>
+        <v>49427</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>28837</v>
+        <v>39145</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>48131</v>
+        <v>60770</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1178184357504436</v>
+        <v>0.131196338761679</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.0910383476845916</v>
+        <v>0.1039049168807791</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.151946242670896</v>
+        <v>0.161304269553879</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>78196</v>
+        <v>100491</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>66218</v>
+        <v>85768</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>92544</v>
+        <v>118939</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.1178883703314369</v>
+        <v>0.1275470801883945</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.09982949766626986</v>
+        <v>0.1088603742255447</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.1395188298049585</v>
+        <v>0.1509617081654223</v>
       </c>
     </row>
     <row r="12">
@@ -1301,67 +1301,67 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>86311</v>
+        <v>104405</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>73763</v>
+        <v>90510</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>98860</v>
+        <v>120221</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.2490595304529671</v>
+        <v>0.2539427313740977</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.2128508629604221</v>
+        <v>0.2201458373863795</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.2852725632501018</v>
+        <v>0.2924135693889763</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>69282</v>
+        <v>84190</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>57397</v>
+        <v>71822</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>81316</v>
+        <v>98994</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.218719062092952</v>
+        <v>0.2234693985952667</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.1811993656104209</v>
+        <v>0.1906406327656618</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2567106366360903</v>
+        <v>0.2627639923140719</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>224</v>
+        <v>272</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>155592</v>
+        <v>188595</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>137521</v>
+        <v>169444</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>172970</v>
+        <v>206938</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.2345704975385737</v>
+        <v>0.2393711944926965</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.2073268044666646</v>
+        <v>0.2150642769011608</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.2607696526757379</v>
+        <v>0.2626531585851949</v>
       </c>
     </row>
     <row r="13">
@@ -1372,67 +1372,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>208</v>
+        <v>261</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>143839</v>
+        <v>180145</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>129340</v>
+        <v>164277</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>160109</v>
+        <v>198238</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4150637956736576</v>
+        <v>0.4381655974419434</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.3732246234880128</v>
+        <v>0.3995694780731541</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.4620128994770003</v>
+        <v>0.4821718134976419</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>238</v>
+        <v>285</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>164343</v>
+        <v>197308</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>148907</v>
+        <v>180835</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>177737</v>
+        <v>213279</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.5188233217241452</v>
+        <v>0.5237229741955293</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.4700911285637812</v>
+        <v>0.4799971837006908</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.5611070485426134</v>
+        <v>0.5661164619045874</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>446</v>
+        <v>546</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>308181</v>
+        <v>377453</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>287971</v>
+        <v>352258</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>330232</v>
+        <v>400645</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.4646139598401618</v>
+        <v>0.4790768584414908</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.434145026505651</v>
+        <v>0.4470983181439305</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.4978577406107361</v>
+        <v>0.5085122078566531</v>
       </c>
     </row>
     <row r="14">
@@ -1449,19 +1449,19 @@
         <v>13571</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>8316</v>
+        <v>8331</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>20686</v>
+        <v>21162</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.03916037635837425</v>
+        <v>0.0330083014475553</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.02399706379325731</v>
+        <v>0.02026394672774205</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.05969322829877921</v>
+        <v>0.05147144068591719</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>16</v>
@@ -1470,19 +1470,19 @@
         <v>10596</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>6461</v>
+        <v>6468</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>16706</v>
+        <v>16346</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.03345082622358003</v>
+        <v>0.02812514606706737</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.02039698681229374</v>
+        <v>0.01716835827490435</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.05273952676769117</v>
+        <v>0.04338896907518623</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>35</v>
@@ -1491,19 +1491,19 @@
         <v>24167</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>17456</v>
+        <v>16934</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>33194</v>
+        <v>32585</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.03643379155922741</v>
+        <v>0.03067330647864851</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.02631710933976018</v>
+        <v>0.02149301588889166</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.05004398757276072</v>
+        <v>0.04135852513961794</v>
       </c>
     </row>
     <row r="15">
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>500</v>
+        <v>592</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>346546</v>
+        <v>411135</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>346546</v>
+        <v>411135</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>346546</v>
+        <v>411135</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -1535,16 +1535,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>457</v>
+        <v>542</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>316761</v>
+        <v>376741</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>316761</v>
+        <v>376741</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>316761</v>
+        <v>376741</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -1556,16 +1556,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>957</v>
+        <v>1134</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>663306</v>
+        <v>787876</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>663306</v>
+        <v>787876</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>663306</v>
+        <v>787876</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -1595,19 +1595,19 @@
         <v>13589</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>8429</v>
+        <v>8335</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>20274</v>
+        <v>21427</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.114049845337112</v>
+        <v>0.09824342770753847</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.07074063552109805</v>
+        <v>0.06026136300727656</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.17015714628773</v>
+        <v>0.1549085758692119</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>16</v>
@@ -1616,19 +1616,19 @@
         <v>11406</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>6849</v>
+        <v>6937</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>18150</v>
+        <v>17259</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.09665616419189561</v>
+        <v>0.08212901799326482</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.05804498381340847</v>
+        <v>0.04995396665921866</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1538130437107371</v>
+        <v>0.1242784804537525</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>34</v>
@@ -1637,19 +1637,19 @@
         <v>24995</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>17523</v>
+        <v>18096</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>33887</v>
+        <v>34088</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.1053949830817877</v>
+        <v>0.09016999737441518</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.07388731523835111</v>
+        <v>0.06528416152618295</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.1428903410775778</v>
+        <v>0.1229737432921887</v>
       </c>
     </row>
     <row r="17">
@@ -1660,67 +1660,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>15114</v>
+        <v>16589</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>9864</v>
+        <v>10867</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>21828</v>
+        <v>23979</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.1268545772258867</v>
+        <v>0.1199357909447701</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.08278364341913261</v>
+        <v>0.07856294635179772</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.1832046934768107</v>
+        <v>0.1733633809473616</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>11022</v>
+        <v>13742</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>6667</v>
+        <v>8203</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>17036</v>
+        <v>21035</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.09340268368741966</v>
+        <v>0.09895162348612535</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.0564975383325583</v>
+        <v>0.05906874842799453</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1443724401041559</v>
+        <v>0.1514635569254963</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>26136</v>
+        <v>30331</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>19002</v>
+        <v>22620</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>35307</v>
+        <v>40386</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.11020936403967</v>
+        <v>0.1094225784176057</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.08012790022646854</v>
+        <v>0.08160520855446832</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.1488772295310471</v>
+        <v>0.1456959501068952</v>
       </c>
     </row>
     <row r="18">
@@ -1731,67 +1731,67 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>34299</v>
+        <v>42195</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>26919</v>
+        <v>34023</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>43606</v>
+        <v>51449</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.2878714474269953</v>
+        <v>0.3050586841629601</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.2259328604816585</v>
+        <v>0.245973841012244</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.3659806687545115</v>
+        <v>0.3719629995594604</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>27594</v>
+        <v>33915</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>20726</v>
+        <v>25935</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>36772</v>
+        <v>43283</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.2338404134123934</v>
+        <v>0.2442080697658539</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.1756416482678465</v>
+        <v>0.1867460846703915</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.3116164609527833</v>
+        <v>0.3116696374781411</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>61893</v>
+        <v>76110</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>51628</v>
+        <v>65078</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>73497</v>
+        <v>90507</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.2609863301821199</v>
+        <v>0.2745721069458231</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.21770149353462</v>
+        <v>0.2347729713106875</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.3099146576495801</v>
+        <v>0.3265117709233709</v>
       </c>
     </row>
     <row r="19">
@@ -1802,67 +1802,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>52616</v>
+        <v>62415</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>43757</v>
+        <v>52547</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>61862</v>
+        <v>72812</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.4416007759955087</v>
+        <v>0.4512443086250386</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.3672476547874734</v>
+        <v>0.3799000301805563</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.5192042297103097</v>
+        <v>0.5264069295612853</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>66621</v>
+        <v>78453</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>58110</v>
+        <v>68439</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>76044</v>
+        <v>88474</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.5645696384003481</v>
+        <v>0.5649132799822062</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.4924489741375972</v>
+        <v>0.4928085701549671</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.6444239384091678</v>
+        <v>0.637069890724108</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>119237</v>
+        <v>140868</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>106824</v>
+        <v>127459</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>131868</v>
+        <v>155033</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.5027884312665444</v>
+        <v>0.5081932467221636</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.4504447378870655</v>
+        <v>0.4598188377106642</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.5560499708194091</v>
+        <v>0.5592941932200262</v>
       </c>
     </row>
     <row r="20">
@@ -1879,19 +1879,19 @@
         <v>3530</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>7807</v>
+        <v>7467</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.02962335401449728</v>
+        <v>0.02551778855969274</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.01053918597728067</v>
+        <v>0.009118125932701501</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.0655241512407604</v>
+        <v>0.05398293243130406</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>2</v>
@@ -1903,16 +1903,16 @@
         <v>0</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>4176</v>
+        <v>4706</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.01153110030794316</v>
+        <v>0.009798008772549785</v>
       </c>
       <c r="O20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.03539202511755218</v>
+        <v>0.03388894973956327</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>7</v>
@@ -1921,19 +1921,19 @@
         <v>4890</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>1966</v>
+        <v>2008</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>9216</v>
+        <v>9037</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.02062089142987811</v>
+        <v>0.01764207053999246</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.008292072169335011</v>
+        <v>0.007243202591405287</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.03886306474032063</v>
+        <v>0.03260322479912747</v>
       </c>
     </row>
     <row r="21">
@@ -1944,16 +1944,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>119148</v>
+        <v>138318</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>119148</v>
+        <v>138318</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>119148</v>
+        <v>138318</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -1965,16 +1965,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>118003</v>
+        <v>138876</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>118003</v>
+        <v>138876</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>118003</v>
+        <v>138876</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -1986,16 +1986,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>335</v>
+        <v>391</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>237152</v>
+        <v>277194</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>237152</v>
+        <v>277194</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>237152</v>
+        <v>277194</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -2025,19 +2025,19 @@
         <v>83574</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>70215</v>
+        <v>71604</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>97655</v>
+        <v>99218</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.1599209690412665</v>
+        <v>0.1336695728679235</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.1343598103058352</v>
+        <v>0.1145257286557508</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.1868666139653269</v>
+        <v>0.1586919324117191</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>80</v>
@@ -2046,19 +2046,19 @@
         <v>54306</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>44362</v>
+        <v>43336</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>67459</v>
+        <v>65959</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1084664916291259</v>
+        <v>0.09108860998299645</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.08860513025758981</v>
+        <v>0.07268877310993178</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1347370218607096</v>
+        <v>0.1106342565805754</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>196</v>
@@ -2067,19 +2067,19 @@
         <v>137879</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>120396</v>
+        <v>119021</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>158675</v>
+        <v>155833</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.1347449208890728</v>
+        <v>0.112885237867469</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.1176584632427466</v>
+        <v>0.09744566564834969</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.1550675385488085</v>
+        <v>0.1275839746814718</v>
       </c>
     </row>
     <row r="23">
@@ -2090,67 +2090,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>63306</v>
+        <v>78210</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>51594</v>
+        <v>65706</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>76192</v>
+        <v>92898</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.1211385091261462</v>
+        <v>0.125090169034883</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.0987268504194669</v>
+        <v>0.1050923338302101</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.1457956930351776</v>
+        <v>0.1485833491110696</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>54901</v>
+        <v>71030</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>43747</v>
+        <v>58829</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>66882</v>
+        <v>86348</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.1096550973152521</v>
+        <v>0.1191403589241443</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.08737726512906233</v>
+        <v>0.09867476264798246</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1335852034172904</v>
+        <v>0.1448337675106713</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>118207</v>
+        <v>149240</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>102789</v>
+        <v>131334</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>136374</v>
+        <v>167568</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.1155198158025925</v>
+        <v>0.1221859874910114</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.1004525650536079</v>
+        <v>0.1075266722351887</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.1332739215027414</v>
+        <v>0.1371922848668591</v>
       </c>
     </row>
     <row r="24">
@@ -2161,67 +2161,67 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>134037</v>
+        <v>163296</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>118362</v>
+        <v>146153</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>149110</v>
+        <v>183647</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.2564839841093964</v>
+        <v>0.2611802597842278</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.2264894924366512</v>
+        <v>0.2337600896929215</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.2853274605365894</v>
+        <v>0.2937292468844643</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>116307</v>
+        <v>141815</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>102241</v>
+        <v>126567</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>132417</v>
+        <v>160317</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.2323030171496264</v>
+        <v>0.237870412302293</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.2042080616132547</v>
+        <v>0.2122944254963693</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.2644795750005397</v>
+        <v>0.2689039442236753</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>359</v>
+        <v>437</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>250344</v>
+        <v>305112</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>229943</v>
+        <v>280512</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>275047</v>
+        <v>330466</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.2446525319372258</v>
+        <v>0.2498024128298666</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.2247151487329857</v>
+        <v>0.2296618816362884</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.2687938991134488</v>
+        <v>0.2705606171504879</v>
       </c>
     </row>
     <row r="25">
@@ -2232,67 +2232,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>323</v>
+        <v>408</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>223948</v>
+        <v>282417</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>206731</v>
+        <v>262417</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>242347</v>
+        <v>302353</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.4285320959053765</v>
+        <v>0.4517043319187743</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.3955861479585481</v>
+        <v>0.4197161879221311</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.4637386695383005</v>
+        <v>0.4835901290856082</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>369</v>
+        <v>446</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>257606</v>
+        <v>311486</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>240625</v>
+        <v>290995</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>276260</v>
+        <v>331750</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.5145216830855965</v>
+        <v>0.5224630132644862</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.480606662493651</v>
+        <v>0.4880927559959314</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.5517803847176144</v>
+        <v>0.5564513623275738</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>692</v>
+        <v>854</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>481553</v>
+        <v>593903</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>455175</v>
+        <v>564185</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>508656</v>
+        <v>623787</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.4706057520052376</v>
+        <v>0.4862425865198763</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.4448270282462575</v>
+        <v>0.4619114124675903</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.4970918865323469</v>
+        <v>0.5107095375833609</v>
       </c>
     </row>
     <row r="26">
@@ -2309,19 +2309,19 @@
         <v>17729</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>11021</v>
+        <v>11746</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>25936</v>
+        <v>25325</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.03392444181781438</v>
+        <v>0.02835566639419143</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.02108821390355955</v>
+        <v>0.01878698858724506</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.04963011069580497</v>
+        <v>0.04050482125234708</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>27</v>
@@ -2330,19 +2330,19 @@
         <v>17550</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>11218</v>
+        <v>11728</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>24693</v>
+        <v>24750</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.0350537108203991</v>
+        <v>0.02943760552608009</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.02240678910564161</v>
+        <v>0.01967173660685467</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.04931933223154731</v>
+        <v>0.04151435620132864</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>52</v>
@@ -2351,19 +2351,19 @@
         <v>35279</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>25768</v>
+        <v>27623</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>44582</v>
+        <v>45683</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.03447697936587126</v>
+        <v>0.02888377529177662</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.02518211219267625</v>
+        <v>0.02261529356299468</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.04356840320039503</v>
+        <v>0.03740168071176733</v>
       </c>
     </row>
     <row r="27">
@@ -2374,16 +2374,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>751</v>
+        <v>895</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>522593</v>
+        <v>625225</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>522593</v>
+        <v>625225</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>522593</v>
+        <v>625225</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -2395,16 +2395,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>718</v>
+        <v>854</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -2416,16 +2416,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>1469</v>
+        <v>1749</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>1023263</v>
+        <v>1221413</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>1023263</v>
+        <v>1221413</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>1023263</v>
+        <v>1221413</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -2496,7 +2496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC recogido por medición en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2016 (tasa de respuesta: 82,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2686,19 +2686,19 @@
         <v>7145</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3522</v>
+        <v>3405</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>11991</v>
+        <v>12014</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.145724685975621</v>
+        <v>0.109077436056161</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.07184133283234623</v>
+        <v>0.0519883670994447</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.2445766696315481</v>
+        <v>0.1834134254689287</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>6</v>
@@ -2707,19 +2707,19 @@
         <v>3841</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>1663</v>
+        <v>1521</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>7595</v>
+        <v>7914</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.09977521743314868</v>
+        <v>0.07470385368678423</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.04318812140279393</v>
+        <v>0.02957826787958148</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1972715162068245</v>
+        <v>0.1539162683753869</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>16</v>
@@ -2728,19 +2728,19 @@
         <v>10986</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>6434</v>
+        <v>6530</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>16536</v>
+        <v>17083</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.125514073240433</v>
+        <v>0.09396072247480433</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.07350258295747258</v>
+        <v>0.05584955028942504</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.1889230851198871</v>
+        <v>0.1461089937533917</v>
       </c>
     </row>
     <row r="5">
@@ -2751,67 +2751,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>4464</v>
+        <v>6286</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2017</v>
+        <v>3013</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>9162</v>
+        <v>11207</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.09105580230084936</v>
+        <v>0.09596580530976236</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.04113061545180495</v>
+        <v>0.04599656374638243</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.1868740643830067</v>
+        <v>0.1710991609654375</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>4976</v>
+        <v>5576</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>2223</v>
+        <v>2576</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>9262</v>
+        <v>10567</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.1292381997483567</v>
+        <v>0.1084453854276133</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.05774365953592382</v>
+        <v>0.05009262900761297</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2405647385431043</v>
+        <v>0.205515904886975</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>9440</v>
+        <v>11862</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>5604</v>
+        <v>7310</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>15402</v>
+        <v>18106</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.1078501129336113</v>
+        <v>0.101454038576517</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.06401990057475185</v>
+        <v>0.06251939935108745</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.17597006921938</v>
+        <v>0.1548586518807044</v>
       </c>
     </row>
     <row r="6">
@@ -2822,67 +2822,67 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>17576</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>11706</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>23836</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.268325890271509</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.1787080305528392</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.3638952966109605</v>
+      </c>
+      <c r="J6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>14359</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>9309</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>20651</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>0.2928679210905411</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>0.1898650139543009</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>0.4211928944961559</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>15</v>
-      </c>
       <c r="K6" s="5" t="n">
-        <v>10071</v>
+        <v>13786</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>6356</v>
+        <v>9103</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>15260</v>
+        <v>19492</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.2615813275254621</v>
+        <v>0.2681104456963617</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.1650868767736276</v>
+        <v>0.177039177472352</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3963750210432227</v>
+        <v>0.3790746592200242</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>24430</v>
+        <v>31362</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>17088</v>
+        <v>24238</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>30862</v>
+        <v>40292</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.2791066906257629</v>
+        <v>0.2682311426859894</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.1952242922875942</v>
+        <v>0.2073043548678956</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.3526009400985147</v>
+        <v>0.3446060551300899</v>
       </c>
     </row>
     <row r="7">
@@ -2893,67 +2893,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>21073</v>
+        <v>32507</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>15483</v>
+        <v>25742</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>26247</v>
+        <v>39434</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4298059674154314</v>
+        <v>0.4962817714044161</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.315783432106042</v>
+        <v>0.3929916011712332</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.5353352848674492</v>
+        <v>0.6020341771946758</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>18094</v>
+        <v>26698</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>12966</v>
+        <v>20987</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>23137</v>
+        <v>32627</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4699913502385768</v>
+        <v>0.5192302758010966</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.3367801802111491</v>
+        <v>0.4081619538211099</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.6009858237119441</v>
+        <v>0.6345300388725803</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>39167</v>
+        <v>59206</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>31955</v>
+        <v>50260</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>47731</v>
+        <v>67053</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.4474812797882645</v>
+        <v>0.5063739975901331</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.3650887212925614</v>
+        <v>0.4298661280127768</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.545325911277228</v>
+        <v>0.5734858996429937</v>
       </c>
     </row>
     <row r="8">
@@ -2970,19 +2970,19 @@
         <v>1988</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>5339</v>
+        <v>5312</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.0405456232175572</v>
+        <v>0.03034909695815143</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.01227540093745525</v>
+        <v>0.009293582170770609</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.1088878695526988</v>
+        <v>0.08109001251167491</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>2</v>
@@ -2994,16 +2994,16 @@
         <v>0</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>5170</v>
+        <v>5674</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.0394139050544557</v>
+        <v>0.02951003938814414</v>
       </c>
       <c r="O8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1343020622030157</v>
+        <v>0.110353883758532</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>5</v>
@@ -3012,19 +3012,19 @@
         <v>3505</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>1256</v>
+        <v>1271</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>8039</v>
+        <v>8174</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.04004784341192832</v>
+        <v>0.02998009867255612</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.01435226280011923</v>
+        <v>0.01086783826162878</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.09184880865181211</v>
+        <v>0.06990630849329589</v>
       </c>
     </row>
     <row r="9">
@@ -3035,16 +3035,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>49029</v>
+        <v>65502</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>49029</v>
+        <v>65502</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>49029</v>
+        <v>65502</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -3056,16 +3056,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>38499</v>
+        <v>51419</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>38499</v>
+        <v>51419</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>38499</v>
+        <v>51419</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -3077,16 +3077,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>87528</v>
+        <v>116921</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>87528</v>
+        <v>116921</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>87528</v>
+        <v>116921</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -3116,19 +3116,19 @@
         <v>34159</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>24948</v>
+        <v>25792</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>43368</v>
+        <v>44502</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.09592639364674721</v>
+        <v>0.08153315460765528</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.07005925225248191</v>
+        <v>0.06156233110255446</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.1217867016313053</v>
+        <v>0.1062183749681222</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>27</v>
@@ -3137,19 +3137,19 @@
         <v>17276</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>11499</v>
+        <v>11393</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>24350</v>
+        <v>24637</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.05129138239919049</v>
+        <v>0.04435504082889473</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.03413917375385223</v>
+        <v>0.02925119145681986</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.07229623985261485</v>
+        <v>0.06325502938743496</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>76</v>
@@ -3158,19 +3158,19 @@
         <v>51435</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>40576</v>
+        <v>41264</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>63674</v>
+        <v>64484</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.07423000317123038</v>
+        <v>0.06362184332336963</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.05855796630116938</v>
+        <v>0.05104136083732067</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.09189338233792292</v>
+        <v>0.07976248653628312</v>
       </c>
     </row>
     <row r="11">
@@ -3181,67 +3181,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>47650</v>
+        <v>60480</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>38077</v>
+        <v>49549</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>59202</v>
+        <v>73712</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.1338110715936445</v>
+        <v>0.1443554767366086</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.1069283523073643</v>
+        <v>0.1182661962962235</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.1662512964951763</v>
+        <v>0.1759388059386902</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>25895</v>
+        <v>28561</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>19046</v>
+        <v>21520</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>34264</v>
+        <v>39358</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.07688192684135824</v>
+        <v>0.07333032651674666</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.05654769725995414</v>
+        <v>0.05525286034152083</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1017279687726694</v>
+        <v>0.101050662585255</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>73545</v>
+        <v>89041</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>60719</v>
+        <v>75784</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>86458</v>
+        <v>104978</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.1061386924576264</v>
+        <v>0.110137668319231</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.08762766152468199</v>
+        <v>0.09373966729065575</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.1247738678962507</v>
+        <v>0.1298511573792143</v>
       </c>
     </row>
     <row r="12">
@@ -3252,67 +3252,67 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>76113</v>
+        <v>92269</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>64621</v>
+        <v>80086</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>89369</v>
+        <v>109050</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.2137406032561625</v>
+        <v>0.2202328611508541</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.1814690751935827</v>
+        <v>0.1911533580665968</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.2509652570229377</v>
+        <v>0.2602851911657007</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>74230</v>
+        <v>83541</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>63144</v>
+        <v>70613</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>88384</v>
+        <v>95966</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2203876145475955</v>
+        <v>0.2144895310404785</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.1874736309744701</v>
+        <v>0.1812977080512742</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2624115364604892</v>
+        <v>0.2463901433494838</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>150343</v>
+        <v>175810</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>132875</v>
+        <v>156966</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>168416</v>
+        <v>196720</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.2169716129152447</v>
+        <v>0.217465895241085</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.1917620734024242</v>
+        <v>0.1941569733581424</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.2430550434811019</v>
+        <v>0.2433295354243006</v>
       </c>
     </row>
     <row r="13">
@@ -3323,67 +3323,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>246</v>
+        <v>294</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>173376</v>
+        <v>207253</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>157172</v>
+        <v>188080</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>189332</v>
+        <v>222928</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4868754447555936</v>
+        <v>0.4946821012185793</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.4413717096620441</v>
+        <v>0.4489179143136075</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.5316811072939484</v>
+        <v>0.5320949928811297</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>307</v>
+        <v>369</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>205302</v>
+        <v>245997</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>190975</v>
+        <v>230646</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>219002</v>
+        <v>261032</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.6095401590248781</v>
+        <v>0.6315923448507439</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.5670032728057679</v>
+        <v>0.5921789292527794</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.6502152166004501</v>
+        <v>0.6701935907116142</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>553</v>
+        <v>663</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>378679</v>
+        <v>453251</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>357614</v>
+        <v>429566</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>398543</v>
+        <v>474909</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.5465008702672715</v>
+        <v>0.5606413913077938</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.5161011876036768</v>
+        <v>0.531345563964112</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.5751682455323792</v>
+        <v>0.5874319143110355</v>
       </c>
     </row>
     <row r="14">
@@ -3400,19 +3400,19 @@
         <v>24801</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>17556</v>
+        <v>16986</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>33534</v>
+        <v>33531</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.06964648674785225</v>
+        <v>0.05919640628630268</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.04930156559922916</v>
+        <v>0.04054214751323427</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.09417017563727184</v>
+        <v>0.08003324821792122</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>22</v>
@@ -3421,19 +3421,19 @@
         <v>14112</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>9058</v>
+        <v>9039</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>20622</v>
+        <v>20616</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.04189891718697761</v>
+        <v>0.03623275676313614</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.02689288581215985</v>
+        <v>0.02320839647288157</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.06122667359949115</v>
+        <v>0.0529307393170363</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>56</v>
@@ -3442,19 +3442,19 @@
         <v>38913</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>29122</v>
+        <v>30855</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>49522</v>
+        <v>51031</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.05615882118862701</v>
+        <v>0.04813320180852064</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.04202885417416471</v>
+        <v>0.03816609065841148</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.07146845258021133</v>
+        <v>0.06312212624143579</v>
       </c>
     </row>
     <row r="15">
@@ -3465,16 +3465,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>503</v>
+        <v>592</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>356100</v>
+        <v>418963</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>356100</v>
+        <v>418963</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>356100</v>
+        <v>418963</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -3486,16 +3486,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>502</v>
+        <v>584</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>336815</v>
+        <v>389487</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>336815</v>
+        <v>389487</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>336815</v>
+        <v>389487</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -3507,16 +3507,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>1005</v>
+        <v>1176</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>692915</v>
+        <v>808450</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>692915</v>
+        <v>808450</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>692915</v>
+        <v>808450</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -3546,19 +3546,19 @@
         <v>8589</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>4633</v>
+        <v>4594</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>14453</v>
+        <v>14385</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.07211962973030034</v>
+        <v>0.05841370658932565</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.03889889244880981</v>
+        <v>0.0312438588617104</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.1213603318339201</v>
+        <v>0.09783175031393412</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>12</v>
@@ -3567,19 +3567,19 @@
         <v>7830</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>4529</v>
+        <v>4591</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>13662</v>
+        <v>13013</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.06998605236016467</v>
+        <v>0.05732962133283753</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.0404827130186967</v>
+        <v>0.03361552775779594</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1221111277077458</v>
+        <v>0.09527470287372787</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>25</v>
@@ -3588,19 +3588,19 @@
         <v>16419</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>10933</v>
+        <v>10656</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>23565</v>
+        <v>23120</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.07108612708088138</v>
+        <v>0.05789163504543349</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.04733551873728374</v>
+        <v>0.03757036704754588</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.1020236641473665</v>
+        <v>0.08151811464370122</v>
       </c>
     </row>
     <row r="17">
@@ -3611,67 +3611,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>10560</v>
+        <v>11323</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>6154</v>
+        <v>6785</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>16665</v>
+        <v>17648</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.08866958512505489</v>
+        <v>0.07701034246828642</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.05167544095701058</v>
+        <v>0.0461456698862717</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.1399364957777372</v>
+        <v>0.1200234288326613</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>7996</v>
+        <v>10979</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>4292</v>
+        <v>6650</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>13290</v>
+        <v>16489</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.07146461734230812</v>
+        <v>0.08038012123415803</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.03835824056982586</v>
+        <v>0.04868845846651488</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.118779474915988</v>
+        <v>0.1207244817266447</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>18556</v>
+        <v>22302</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>12425</v>
+        <v>15638</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>25954</v>
+        <v>31734</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.08033551670291664</v>
+        <v>0.07863315358239818</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.05379241664031621</v>
+        <v>0.05513583202175765</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.1123650310788288</v>
+        <v>0.1118888804929185</v>
       </c>
     </row>
     <row r="18">
@@ -3682,67 +3682,67 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>34761</v>
+        <v>46233</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>26713</v>
+        <v>36930</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>43443</v>
+        <v>55154</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.291886153609514</v>
+        <v>0.3144384079269376</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.2243033903015852</v>
+        <v>0.251162456829886</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.3647889382305543</v>
+        <v>0.3751106098828756</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>17372</v>
+        <v>25538</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>12070</v>
+        <v>18514</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>23730</v>
+        <v>33462</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1552663214130268</v>
+        <v>0.1869729029262056</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.1078770689690354</v>
+        <v>0.1355512096537432</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2120915235607094</v>
+        <v>0.2449875569738253</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>52133</v>
+        <v>71771</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>42468</v>
+        <v>60729</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>63453</v>
+        <v>85607</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.2257076496027605</v>
+        <v>0.2530538326913128</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.1838625709895773</v>
+        <v>0.214118589939755</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.2747157408075558</v>
+        <v>0.3018362822097524</v>
       </c>
     </row>
     <row r="19">
@@ -3753,67 +3753,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>60526</v>
+        <v>76234</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>51753</v>
+        <v>66638</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>69291</v>
+        <v>85003</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.5082312432128516</v>
+        <v>0.5184736295486186</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.4345609412838436</v>
+        <v>0.4532084279192781</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.5818261887331105</v>
+        <v>0.5781161166283789</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>75307</v>
+        <v>88858</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>67021</v>
+        <v>79138</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>82952</v>
+        <v>97600</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.673073687643558</v>
+        <v>0.6505711530986588</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.5990129575494735</v>
+        <v>0.5794036948315175</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.7414013990900356</v>
+        <v>0.7145711949939321</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>198</v>
+        <v>241</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>135833</v>
+        <v>165093</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>122549</v>
+        <v>152373</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>147540</v>
+        <v>178219</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.5880807511053159</v>
+        <v>0.5820888827322198</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.5305693647016254</v>
+        <v>0.5372418654862464</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.6387648578985898</v>
+        <v>0.6283719163341419</v>
       </c>
     </row>
     <row r="20">
@@ -3830,19 +3830,19 @@
         <v>4656</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1472</v>
+        <v>2062</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>9022</v>
+        <v>9473</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.03909338832227906</v>
+        <v>0.03166391346683178</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.01235966800881311</v>
+        <v>0.01402265283654001</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.07575253050968088</v>
+        <v>0.0644271054747706</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>5</v>
@@ -3851,19 +3851,19 @@
         <v>3380</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1320</v>
+        <v>1325</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>7776</v>
+        <v>7448</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.03020932124094238</v>
+        <v>0.02474620140814008</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.01180148811574455</v>
+        <v>0.009697577164316839</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.06949944030256813</v>
+        <v>0.05453360380031239</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>11</v>
@@ -3872,19 +3872,19 @@
         <v>8036</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>4188</v>
+        <v>4079</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>13376</v>
+        <v>14387</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.03478995550812557</v>
+        <v>0.0283324959486357</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.0181328404354169</v>
+        <v>0.01438284461287964</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.05791028917402919</v>
+        <v>0.05072652811081869</v>
       </c>
     </row>
     <row r="21">
@@ -3895,16 +3895,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>172</v>
+        <v>212</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>119092</v>
+        <v>147035</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>119092</v>
+        <v>147035</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>119092</v>
+        <v>147035</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -3916,16 +3916,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>111885</v>
+        <v>136585</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>111885</v>
+        <v>136585</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>111885</v>
+        <v>136585</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -3937,16 +3937,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>339</v>
+        <v>416</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>230977</v>
+        <v>283621</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>230977</v>
+        <v>283621</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>230977</v>
+        <v>283621</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -3976,19 +3976,19 @@
         <v>49893</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>40373</v>
+        <v>39257</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>62860</v>
+        <v>61263</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.09517553857995151</v>
+        <v>0.0790071602179829</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.07701526912698325</v>
+        <v>0.0621653092029538</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.1199111714694741</v>
+        <v>0.09701254255830065</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>45</v>
@@ -3997,19 +3997,19 @@
         <v>28947</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>21942</v>
+        <v>21330</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>38638</v>
+        <v>37770</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.05941582670356314</v>
+        <v>0.05012595175945889</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.04503704017761716</v>
+        <v>0.03693643464520396</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.07930639473648537</v>
+        <v>0.06540279238725248</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>117</v>
@@ -4018,19 +4018,19 @@
         <v>78840</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>65138</v>
+        <v>66489</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>94282</v>
+        <v>94830</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.07795015668913016</v>
+        <v>0.06521164604088794</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.06440288371088079</v>
+        <v>0.05499520384656755</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.09321717571063129</v>
+        <v>0.07843698128650946</v>
       </c>
     </row>
     <row r="23">
@@ -4041,67 +4041,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>62674</v>
+        <v>78089</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>51193</v>
+        <v>64799</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>75448</v>
+        <v>93247</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.1195570572329769</v>
+        <v>0.1236559899370605</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.09765447306179886</v>
+        <v>0.1026112336879394</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.1439241473673319</v>
+        <v>0.1476601083961345</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>38866</v>
+        <v>45116</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>29688</v>
+        <v>35743</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>49259</v>
+        <v>55714</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.07977506961950961</v>
+        <v>0.07812431973573913</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.06093624757692553</v>
+        <v>0.06189315751584948</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1011070846613938</v>
+        <v>0.09647590010222286</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>101541</v>
+        <v>123205</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>86375</v>
+        <v>106465</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>117697</v>
+        <v>140019</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.1003941531417287</v>
+        <v>0.101907149244636</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.08539951592246428</v>
+        <v>0.08806077074210729</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.1163683341045885</v>
+        <v>0.115814276570345</v>
       </c>
     </row>
     <row r="24">
@@ -4112,67 +4112,67 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>177</v>
+        <v>222</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>125233</v>
+        <v>156079</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>110034</v>
+        <v>140160</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>140312</v>
+        <v>174687</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.23889425466918</v>
+        <v>0.2471556176340138</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.2099005159746317</v>
+        <v>0.2219472729403012</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.2676580452636066</v>
+        <v>0.2766229547962112</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>101672</v>
+        <v>122865</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>87514</v>
+        <v>107239</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>116604</v>
+        <v>139031</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.2086876950611254</v>
+        <v>0.2127557961254483</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.1796266552291893</v>
+        <v>0.1856983703716776</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.239335498468346</v>
+        <v>0.2407488064247911</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>325</v>
+        <v>403</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>226906</v>
+        <v>278944</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>205350</v>
+        <v>257609</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>249456</v>
+        <v>305661</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.2243438151506738</v>
+        <v>0.2307240605545215</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.2030314735056603</v>
+        <v>0.2130775566749106</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.2466391477760726</v>
+        <v>0.2528231540567366</v>
       </c>
     </row>
     <row r="25">
@@ -4183,67 +4183,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>364</v>
+        <v>450</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>254976</v>
+        <v>315995</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>235846</v>
+        <v>296682</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>272198</v>
+        <v>336092</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.4863894319041682</v>
+        <v>0.5003875219920444</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.4498971789407189</v>
+        <v>0.469805520337693</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.5192433282162127</v>
+        <v>0.5322118045669378</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>445</v>
+        <v>540</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>298703</v>
+        <v>361554</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>281624</v>
+        <v>342785</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>315262</v>
+        <v>380221</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.6131033684668857</v>
+        <v>0.6260765010018331</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.5780478453230969</v>
+        <v>0.5935761286545423</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.6470898548161683</v>
+        <v>0.6584007070238873</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>809</v>
+        <v>990</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>553679</v>
+        <v>677549</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>528303</v>
+        <v>650816</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>579459</v>
+        <v>708883</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.5474272824250871</v>
+        <v>0.5604246251598093</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.5223376615531508</v>
+        <v>0.53831271524308</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.5729154089105897</v>
+        <v>0.5863415003871727</v>
       </c>
     </row>
     <row r="26">
@@ -4260,19 +4260,19 @@
         <v>31445</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>23399</v>
+        <v>22996</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>41548</v>
+        <v>42177</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.05998371761372345</v>
+        <v>0.0497937102188984</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.04463589268295169</v>
+        <v>0.03641539584030222</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.07925688276476886</v>
+        <v>0.06678878240000873</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>29</v>
@@ -4281,19 +4281,19 @@
         <v>19010</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>13339</v>
+        <v>13002</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>26892</v>
+        <v>26864</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.03901804014891608</v>
+        <v>0.03291743137752063</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.02737838002734913</v>
+        <v>0.02251391871343842</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.05519763710299874</v>
+        <v>0.04651842499133328</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>72</v>
@@ -4302,19 +4302,19 @@
         <v>50454</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>40692</v>
+        <v>39663</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>62231</v>
+        <v>63180</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.04988459259338034</v>
+        <v>0.04173251900014519</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.0402323219481169</v>
+        <v>0.03280642049981401</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.06152805684246164</v>
+        <v>0.05225813357009278</v>
       </c>
     </row>
     <row r="27">
@@ -4325,16 +4325,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>745</v>
+        <v>897</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -4346,16 +4346,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>726</v>
+        <v>864</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -4367,16 +4367,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>1471</v>
+        <v>1761</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -4447,7 +4447,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC recogido por medición en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2023 (tasa de respuesta: 82,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4661,16 +4661,16 @@
         <v>0</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>2709</v>
+        <v>2624</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.04505723887726167</v>
+        <v>0.03887967230243204</v>
       </c>
       <c r="O4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1628794769386989</v>
+        <v>0.1361212582284047</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>4</v>
@@ -4679,19 +4679,19 @@
         <v>1960</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>431</v>
+        <v>630</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>5740</v>
+        <v>5599</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.04761574264348394</v>
+        <v>0.04474264628279522</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.01047861895876535</v>
+        <v>0.01438941704098809</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.1394551680179995</v>
+        <v>0.1278234520295772</v>
       </c>
     </row>
     <row r="5">
@@ -4723,46 +4723,46 @@
         <v>0.2898617299973336</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>870</v>
+        <v>2262</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0</v>
+        <v>569</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>4899</v>
+        <v>5914</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.05231235193383713</v>
+        <v>0.1173574317611342</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0</v>
+        <v>0.02950718857979113</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2945307315789132</v>
+        <v>0.3067738690584226</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>4067</v>
+        <v>5459</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>1633</v>
+        <v>2397</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>9318</v>
+        <v>10873</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.09881513640800604</v>
+        <v>0.1246352315767758</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.03966941158336591</v>
+        <v>0.05473280725987017</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.2264063737956888</v>
+        <v>0.2482294796746432</v>
       </c>
     </row>
     <row r="6">
@@ -4794,46 +4794,46 @@
         <v>0.4602493370726162</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>3162</v>
+        <v>3531</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>848</v>
+        <v>1163</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>6383</v>
+        <v>7015</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.1900885980026011</v>
+        <v>0.1831727296311567</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.05095165445954208</v>
+        <v>0.06030541315381076</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3837029247503468</v>
+        <v>0.3639075827339708</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>9259</v>
+        <v>9628</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>5398</v>
+        <v>5412</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>14415</v>
+        <v>14519</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.2249569589606011</v>
+        <v>0.219809388116869</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.1311560269552473</v>
+        <v>0.1235480917830112</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.3502387524547632</v>
+        <v>0.331486951009882</v>
       </c>
     </row>
     <row r="7">
@@ -4865,46 +4865,46 @@
         <v>0.7077059731940183</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>11852</v>
+        <v>12734</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>8419</v>
+        <v>8879</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>14584</v>
+        <v>15774</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.7125418111863001</v>
+        <v>0.6605901663052776</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5061151613774948</v>
+        <v>0.4605922191840145</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.8767674784929985</v>
+        <v>0.8182612199783604</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>24894</v>
+        <v>25775</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>19709</v>
+        <v>20250</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>30015</v>
+        <v>30960</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.6048278386165152</v>
+        <v>0.5884635379677567</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.4788600657282821</v>
+        <v>0.4623085069902979</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.7292567969295346</v>
+        <v>0.7068377279967808</v>
       </c>
     </row>
     <row r="8">
@@ -4958,16 +4958,16 @@
         <v>0</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>3421</v>
+        <v>3513</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.02378432337139372</v>
+        <v>0.02234919605580315</v>
       </c>
       <c r="V8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.08311398725665527</v>
+        <v>0.08020190923473529</v>
       </c>
     </row>
     <row r="9">
@@ -4999,16 +4999,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>16634</v>
+        <v>19277</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>16634</v>
+        <v>19277</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>16634</v>
+        <v>19277</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -5020,16 +5020,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>41158</v>
+        <v>43801</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>41158</v>
+        <v>43801</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>41158</v>
+        <v>43801</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -5059,19 +5059,19 @@
         <v>17238</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>12283</v>
+        <v>11805</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>24816</v>
+        <v>25019</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.08605854682158597</v>
+        <v>0.08192887988709142</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.06132091641001077</v>
+        <v>0.05610855874230114</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.1238920390676137</v>
+        <v>0.1189156038466401</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>14</v>
@@ -5080,19 +5080,19 @@
         <v>8062</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>4329</v>
+        <v>4462</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>14258</v>
+        <v>13805</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.05332045049171585</v>
+        <v>0.05054664304932776</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.02863419040776759</v>
+        <v>0.02797879459084111</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.09430147606677493</v>
+        <v>0.08655906085025745</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>44</v>
@@ -5101,19 +5101,19 @@
         <v>25299</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>17958</v>
+        <v>18916</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>33990</v>
+        <v>33824</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.07197646866696639</v>
+        <v>0.0683973355689895</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.05108996765024136</v>
+        <v>0.05114140948482957</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.09670315415105195</v>
+        <v>0.09144579138776139</v>
       </c>
     </row>
     <row r="11">
@@ -5124,67 +5124,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>29935</v>
+        <v>30391</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>21979</v>
+        <v>22146</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>39615</v>
+        <v>40482</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.1494527381662681</v>
+        <v>0.1444444629920905</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.1097310798402318</v>
+        <v>0.1052609557668698</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.1977773360740243</v>
+        <v>0.1924067870305802</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>11659</v>
+        <v>12165</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>6857</v>
+        <v>7842</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>17569</v>
+        <v>18797</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.07711567524972691</v>
+        <v>0.07627722037094738</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.04535401122832314</v>
+        <v>0.0491674995443753</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1162012021714923</v>
+        <v>0.1178559025308136</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>41595</v>
+        <v>42556</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>32143</v>
+        <v>32414</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>53062</v>
+        <v>54815</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.1183374233598617</v>
+        <v>0.1150517823702672</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.09144728577185017</v>
+        <v>0.08763264398226495</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.1509607984744322</v>
+        <v>0.1481952888537808</v>
       </c>
     </row>
     <row r="12">
@@ -5195,67 +5195,67 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>43135</v>
+        <v>47162</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>32679</v>
+        <v>35928</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>56226</v>
+        <v>61553</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.2153535867124656</v>
+        <v>0.2241604042437976</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.1631493072261575</v>
+        <v>0.1707627113250382</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.2807074650301888</v>
+        <v>0.2925574016228613</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>21904</v>
+        <v>24417</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>16063</v>
+        <v>17962</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>30054</v>
+        <v>32424</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.1448734802932465</v>
+        <v>0.153096372556759</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.1062410387966173</v>
+        <v>0.1126218646225816</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.1987811379157658</v>
+        <v>0.2033023113375793</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>65039</v>
+        <v>71580</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>52992</v>
+        <v>58564</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>81701</v>
+        <v>86468</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.185037029606004</v>
+        <v>0.1935186721337711</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.1507639716949248</v>
+        <v>0.1583310036941983</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.2324415087943186</v>
+        <v>0.2337710538295316</v>
       </c>
     </row>
     <row r="13">
@@ -5266,67 +5266,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>99631</v>
+        <v>105245</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>86232</v>
+        <v>91556</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>112397</v>
+        <v>118937</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4974098021590777</v>
+        <v>0.5002230552050941</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.43051453566768</v>
+        <v>0.4351589775768784</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.5611433095130852</v>
+        <v>0.565300550883679</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>102802</v>
+        <v>108079</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>93038</v>
+        <v>98693</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>111458</v>
+        <v>117159</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.6799428968198397</v>
+        <v>0.6776600968088947</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.6153619919724312</v>
+        <v>0.6188055348150671</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.737197190629916</v>
+        <v>0.7345871369451379</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>202433</v>
+        <v>213324</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>185395</v>
+        <v>194764</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>218901</v>
+        <v>228732</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.5759252197605634</v>
+        <v>0.5767312150455519</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.5274506078829875</v>
+        <v>0.5265531862510638</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.6227759900369325</v>
+        <v>0.6183860302693346</v>
       </c>
     </row>
     <row r="14">
@@ -5343,19 +5343,19 @@
         <v>10361</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>6159</v>
+        <v>6369</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>16522</v>
+        <v>16974</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.05172532614060281</v>
+        <v>0.04924319767192625</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.03074858014185625</v>
+        <v>0.03027267799820028</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.08248729281879481</v>
+        <v>0.08067682527204731</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>11</v>
@@ -5364,19 +5364,19 @@
         <v>6765</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>3493</v>
+        <v>3183</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>12007</v>
+        <v>11366</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.04474749714547119</v>
+        <v>0.0424196672140712</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.02310157413829508</v>
+        <v>0.01995950822124562</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.07941868556704196</v>
+        <v>0.0712640607438253</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>26</v>
@@ -5385,19 +5385,19 @@
         <v>17126</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>11688</v>
+        <v>11606</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>24913</v>
+        <v>24821</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.04872385860660451</v>
+        <v>0.0463009948814204</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.03325156606548411</v>
+        <v>0.0313760779291909</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.07087924854748733</v>
+        <v>0.06710413168970604</v>
       </c>
     </row>
     <row r="15">
@@ -5408,16 +5408,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>200300</v>
+        <v>210396</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>200300</v>
+        <v>210396</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>200300</v>
+        <v>210396</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -5429,16 +5429,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>151192</v>
+        <v>159489</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>151192</v>
+        <v>159489</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>151192</v>
+        <v>159489</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -5450,16 +5450,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>351492</v>
+        <v>369885</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>351492</v>
+        <v>369885</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>351492</v>
+        <v>369885</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -5489,19 +5489,19 @@
         <v>2087</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>459</v>
+        <v>481</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>5211</v>
+        <v>5577</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.02960079381458581</v>
+        <v>0.02782004257247526</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.006509778003492194</v>
+        <v>0.00641562101224337</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.07392534627371303</v>
+        <v>0.07435717998415051</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>2</v>
@@ -5513,37 +5513,37 @@
         <v>0</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>3284</v>
+        <v>3677</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.01488906229718835</v>
+        <v>0.01457071741198848</v>
       </c>
       <c r="O16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.04836401694790018</v>
+        <v>0.05300158590952123</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>6</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>3097</v>
+        <v>3098</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>1319</v>
+        <v>1254</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>6823</v>
+        <v>6940</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.02238281562823935</v>
+        <v>0.02145336734370605</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.009531345345509739</v>
+        <v>0.008687481625955668</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.04930386629640419</v>
+        <v>0.04806761898356437</v>
       </c>
     </row>
     <row r="17">
@@ -5560,19 +5560,19 @@
         <v>5272</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>2486</v>
+        <v>2476</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>10270</v>
+        <v>9985</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.07478351708783637</v>
+        <v>0.07028462284271179</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.03526748893718306</v>
+        <v>0.03301099521011785</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.1456954827648413</v>
+        <v>0.1331316443971093</v>
       </c>
       <c r="J17" s="5" t="n">
         <v>9</v>
@@ -5581,40 +5581,40 @@
         <v>5287</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>2481</v>
+        <v>2382</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>9846</v>
+        <v>9836</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.07786772511271016</v>
+        <v>0.07620282563704193</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.03653972809577082</v>
+        <v>0.03433909056013905</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1450173851791606</v>
+        <v>0.1417665089060615</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>17</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>10558</v>
+        <v>10559</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>6035</v>
+        <v>6287</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>16646</v>
+        <v>16526</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.07629671396879956</v>
+        <v>0.07312848656204027</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.04360622414029809</v>
+        <v>0.04354491750333218</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.1202858409171244</v>
+        <v>0.1144602103238487</v>
       </c>
     </row>
     <row r="18">
@@ -5625,67 +5625,67 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>13168</v>
+        <v>14631</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>7807</v>
+        <v>9272</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>19974</v>
+        <v>21712</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.1868039238810769</v>
+        <v>0.1950737883470745</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.1107486053265537</v>
+        <v>0.123621553510369</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.283349335866878</v>
+        <v>0.2894879363970873</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>12880</v>
+        <v>13499</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>8151</v>
+        <v>8449</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>18972</v>
+        <v>19142</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1896953183515948</v>
+        <v>0.1945720859818827</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.1200495373993539</v>
+        <v>0.1217745864408783</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2794313262544287</v>
+        <v>0.2758948568172506</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>26048</v>
+        <v>28131</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>19183</v>
+        <v>20859</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>35204</v>
+        <v>37471</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.1882225211543919</v>
+        <v>0.1948327061800968</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.1386200673666238</v>
+        <v>0.1444730025991444</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.254388335004078</v>
+        <v>0.2595236148181638</v>
       </c>
     </row>
     <row r="19">
@@ -5696,67 +5696,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>48008</v>
+        <v>51057</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>40798</v>
+        <v>43498</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>54454</v>
+        <v>57636</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.6810556197169022</v>
+        <v>0.6807351799637987</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.5787659482511768</v>
+        <v>0.5799488128036949</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.7724901487640922</v>
+        <v>0.768453545613431</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>43739</v>
+        <v>44603</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>37193</v>
+        <v>37526</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>50027</v>
+        <v>50489</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.6442116666792566</v>
+        <v>0.6428861543750236</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.5477920640488847</v>
+        <v>0.5408705121188634</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.7368154267982752</v>
+        <v>0.7277210029368649</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>91748</v>
+        <v>95661</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>81229</v>
+        <v>85459</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>101341</v>
+        <v>104965</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.6629789678278971</v>
+        <v>0.6625476533743121</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.5869694147694375</v>
+        <v>0.591888911692325</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.7322994782143963</v>
+        <v>0.7269918397232549</v>
       </c>
     </row>
     <row r="20">
@@ -5773,19 +5773,19 @@
         <v>1957</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>354</v>
+        <v>608</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>6224</v>
+        <v>5657</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.02775614549959882</v>
+        <v>0.0260863662739398</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.005027323330441692</v>
+        <v>0.008107511951679471</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.08829776158526785</v>
+        <v>0.07541902384722396</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>7</v>
@@ -5794,19 +5794,19 @@
         <v>4979</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>2242</v>
+        <v>2279</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>9494</v>
+        <v>9650</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.07333622755924997</v>
+        <v>0.07176821659406317</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.03302236434577437</v>
+        <v>0.0328457332040991</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.139832642358089</v>
+        <v>0.1390894611977145</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>10</v>
@@ -5815,19 +5815,19 @@
         <v>6936</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>3517</v>
+        <v>3466</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>12161</v>
+        <v>12729</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.05011898142067225</v>
+        <v>0.04803778653984464</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.02541575927738119</v>
+        <v>0.02400837305010166</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.08787543065830818</v>
+        <v>0.08815813389599191</v>
       </c>
     </row>
     <row r="21">
@@ -5838,16 +5838,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>70491</v>
+        <v>75003</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>70491</v>
+        <v>75003</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>70491</v>
+        <v>75003</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -5859,16 +5859,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>67896</v>
+        <v>69380</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>67896</v>
+        <v>69380</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>67896</v>
+        <v>69380</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -5880,16 +5880,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>138387</v>
+        <v>144383</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>138387</v>
+        <v>144383</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>138387</v>
+        <v>144383</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -5919,19 +5919,19 @@
         <v>20534</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>14690</v>
+        <v>14668</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>28221</v>
+        <v>28648</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.06953390192572956</v>
+        <v>0.06625640786564475</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.04974470096925213</v>
+        <v>0.04732664215100515</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.09556382909035477</v>
+        <v>0.09243540000168564</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>18</v>
@@ -5940,19 +5940,19 @@
         <v>9822</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>6252</v>
+        <v>6112</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>16148</v>
+        <v>15770</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.0416677266128314</v>
+        <v>0.03958166673163325</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.02652186616797624</v>
+        <v>0.02463225465861525</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.06850521387435003</v>
+        <v>0.06355012519379581</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>54</v>
@@ -5961,19 +5961,19 @@
         <v>30356</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>23444</v>
+        <v>22751</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>39880</v>
+        <v>40671</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.05716438104834843</v>
+        <v>0.05439547780552147</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.04414723682411792</v>
+        <v>0.04076678787864166</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.07509782334277179</v>
+        <v>0.0728779563978285</v>
       </c>
     </row>
     <row r="23">
@@ -5984,67 +5984,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>38404</v>
+        <v>38859</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>28527</v>
+        <v>29036</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>50639</v>
+        <v>50262</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.1300435512930515</v>
+        <v>0.1253826275996551</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.09659704987445564</v>
+        <v>0.09368918503665173</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.1714747123912722</v>
+        <v>0.1621744021396123</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>17816</v>
+        <v>19715</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>12429</v>
+        <v>13671</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>25125</v>
+        <v>27406</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.0755820387610764</v>
+        <v>0.07944766491378347</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.05272909074143504</v>
+        <v>0.05509119256880767</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.106588504114853</v>
+        <v>0.1104442992135937</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>56220</v>
+        <v>58573</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>44152</v>
+        <v>46838</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>68548</v>
+        <v>74002</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.1058686220566662</v>
+        <v>0.1049576353946957</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.08314327611838998</v>
+        <v>0.08392922356806012</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.1290829566725376</v>
+        <v>0.1326035533823718</v>
       </c>
     </row>
     <row r="24">
@@ -6055,67 +6055,67 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>62400</v>
+        <v>67890</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>48531</v>
+        <v>55392</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>75793</v>
+        <v>83600</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.2113003858910899</v>
+        <v>0.2190557688248159</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.164335334888596</v>
+        <v>0.178727015457265</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.256651485697376</v>
+        <v>0.2697440014259118</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>37945</v>
+        <v>41447</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>29471</v>
+        <v>32069</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>47944</v>
+        <v>52126</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1609744069706351</v>
+        <v>0.167029156973045</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.1250255696228268</v>
+        <v>0.1292330552311124</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.2033911687154394</v>
+        <v>0.2100633209706814</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>100345</v>
+        <v>109338</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>83059</v>
+        <v>93769</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>118421</v>
+        <v>126869</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.1889611793103047</v>
+        <v>0.1959221233532868</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.156409015417359</v>
+        <v>0.168024990941516</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.2229990886652395</v>
+        <v>0.2273362364275305</v>
       </c>
     </row>
     <row r="25">
@@ -6126,67 +6126,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>160681</v>
+        <v>169343</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>144308</v>
+        <v>152814</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>176241</v>
+        <v>184409</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.5440988934224992</v>
+        <v>0.5464041087557022</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.4886578117298992</v>
+        <v>0.4930720308199934</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.5967897434437842</v>
+        <v>0.5950156463513958</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>158394</v>
+        <v>165416</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>145401</v>
+        <v>152685</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>169255</v>
+        <v>177527</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.6719513642623731</v>
+        <v>0.6666114680741072</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.6168306448377638</v>
+        <v>0.6153068377831784</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.718029723597495</v>
+        <v>0.7154177957999903</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>456</v>
+        <v>478</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>319074</v>
+        <v>334760</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>298465</v>
+        <v>313566</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>338554</v>
+        <v>354650</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.6008513465137771</v>
+        <v>0.5998543399847426</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.5620420632921627</v>
+        <v>0.5618777088463388</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.6375338940584754</v>
+        <v>0.6354953173549994</v>
       </c>
     </row>
     <row r="26">
@@ -6203,19 +6203,19 @@
         <v>13296</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>7812</v>
+        <v>8334</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>20024</v>
+        <v>20131</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.04502326746762988</v>
+        <v>0.04290108695418218</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.0264528256244437</v>
+        <v>0.02689121781838753</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.06780558474788687</v>
+        <v>0.06495411129809432</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>18</v>
@@ -6224,19 +6224,19 @@
         <v>11745</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>6950</v>
+        <v>7088</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>18212</v>
+        <v>18088</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.04982446339308403</v>
+        <v>0.04733004330743118</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.02948546523285228</v>
+        <v>0.02856431169621518</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.07726193854317108</v>
+        <v>0.07289368183372605</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>38</v>
@@ -6245,19 +6245,19 @@
         <v>25041</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>18195</v>
+        <v>18189</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>34256</v>
+        <v>34330</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.04715447107090347</v>
+        <v>0.04487042346175357</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.03426226470648568</v>
+        <v>0.03259221294144463</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.06450687227250496</v>
+        <v>0.0615152764375396</v>
       </c>
     </row>
     <row r="27">
@@ -6268,16 +6268,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -6289,16 +6289,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>235722</v>
+        <v>248145</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>235722</v>
+        <v>248145</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>235722</v>
+        <v>248145</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -6310,16 +6310,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>765</v>
+        <v>804</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>531037</v>
+        <v>558068</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>531037</v>
+        <v>558068</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>531037</v>
+        <v>558068</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
